--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104512_W6.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104512_W6.xlsx
@@ -565,67 +565,67 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.3501</v>
+        <v>4.8368</v>
       </c>
       <c r="E2" t="n">
-        <v>3.3623</v>
+        <v>3.3212</v>
       </c>
       <c r="F2" t="n">
-        <v>1.9878</v>
+        <v>1.5156</v>
       </c>
       <c r="G2" t="n">
-        <v>3.2977</v>
+        <v>3.2804</v>
       </c>
       <c r="H2" t="n">
-        <v>2.2688</v>
+        <v>2.2417</v>
       </c>
       <c r="I2" t="n">
-        <v>1.029</v>
+        <v>1.0387</v>
       </c>
       <c r="J2" t="n">
-        <v>2.684</v>
+        <v>2.6455</v>
       </c>
       <c r="K2" t="n">
-        <v>2.0496</v>
+        <v>2.0125</v>
       </c>
       <c r="L2" t="n">
-        <v>0.6344</v>
+        <v>0.633</v>
       </c>
       <c r="M2" t="n">
-        <v>0.6138</v>
+        <v>0.6349</v>
       </c>
       <c r="N2" t="n">
-        <v>0.2192</v>
+        <v>0.2292</v>
       </c>
       <c r="O2" t="n">
-        <v>0.3946</v>
+        <v>0.4057</v>
       </c>
       <c r="P2" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="Q2" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="R2" t="n">
-        <v>1.8147</v>
+        <v>1.8211</v>
       </c>
       <c r="S2" t="n">
-        <v>0.4645</v>
+        <v>-0.037</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.1875</v>
+        <v>-0.1862</v>
       </c>
       <c r="U2" t="n">
-        <v>0.652</v>
+        <v>0.1492</v>
       </c>
       <c r="V2" t="n">
         <v>0</v>
       </c>
       <c r="W2" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X2" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="3">
@@ -643,67 +643,67 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.613</v>
+        <v>3.0025</v>
       </c>
       <c r="E3" t="n">
-        <v>0.6266</v>
+        <v>-0.08409999999999999</v>
       </c>
       <c r="F3" t="n">
-        <v>2.9864</v>
+        <v>3.0866</v>
       </c>
       <c r="G3" t="n">
-        <v>1.4673</v>
+        <v>1.4794</v>
       </c>
       <c r="H3" t="n">
-        <v>0.4517</v>
+        <v>0.451</v>
       </c>
       <c r="I3" t="n">
-        <v>1.0157</v>
+        <v>1.0284</v>
       </c>
       <c r="J3" t="n">
-        <v>1.1221</v>
+        <v>1.1035</v>
       </c>
       <c r="K3" t="n">
-        <v>0.9728</v>
+        <v>0.9545</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1493</v>
+        <v>0.1489</v>
       </c>
       <c r="M3" t="n">
-        <v>0.3452</v>
+        <v>0.3759</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.5212</v>
+        <v>-0.5036</v>
       </c>
       <c r="O3" t="n">
-        <v>0.8663999999999999</v>
+        <v>0.8794999999999999</v>
       </c>
       <c r="P3" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R3" t="n">
-        <v>2.4952</v>
+        <v>2.5039</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.5329</v>
+        <v>-1.1613</v>
       </c>
       <c r="T3" t="n">
-        <v>0.4779</v>
+        <v>-0.2072</v>
       </c>
       <c r="U3" t="n">
-        <v>-1.0108</v>
+        <v>-0.9542</v>
       </c>
       <c r="V3" t="n">
-        <v>1.3176</v>
+        <v>1.3187</v>
       </c>
       <c r="W3" t="n">
-        <v>0.1607</v>
+        <v>0.1578</v>
       </c>
       <c r="X3" t="n">
-        <v>1.1568</v>
+        <v>1.1609</v>
       </c>
     </row>
     <row r="4">
@@ -721,67 +721,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.6791</v>
+        <v>2.2327</v>
       </c>
       <c r="E4" t="n">
-        <v>1.0885</v>
+        <v>1.4958</v>
       </c>
       <c r="F4" t="n">
-        <v>0.5906</v>
+        <v>0.7369</v>
       </c>
       <c r="G4" t="n">
-        <v>1.6701</v>
+        <v>1.6695</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.5556</v>
+        <v>-0.5544</v>
       </c>
       <c r="I4" t="n">
-        <v>2.2257</v>
+        <v>2.2239</v>
       </c>
       <c r="J4" t="n">
-        <v>1.9414</v>
+        <v>1.9257</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.1456</v>
+        <v>-0.1519</v>
       </c>
       <c r="L4" t="n">
-        <v>2.087</v>
+        <v>2.0776</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.2712</v>
+        <v>-0.2562</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.4099</v>
+        <v>-0.4025</v>
       </c>
       <c r="O4" t="n">
-        <v>0.1387</v>
+        <v>0.1463</v>
       </c>
       <c r="P4" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="R4" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.352</v>
+        <v>0.1974</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.6261</v>
+        <v>-0.2023</v>
       </c>
       <c r="U4" t="n">
-        <v>0.274</v>
+        <v>0.3997</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.5463</v>
+        <v>-0.5447</v>
       </c>
       <c r="W4" t="n">
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.5463</v>
+        <v>-0.5447</v>
       </c>
     </row>
     <row r="5">
@@ -799,64 +799,64 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.7256</v>
+        <v>0.555</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.4868</v>
+        <v>-0.7351</v>
       </c>
       <c r="F5" t="n">
-        <v>1.2124</v>
+        <v>1.2901</v>
       </c>
       <c r="G5" t="n">
-        <v>0.4173</v>
+        <v>0.4228</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.505</v>
+        <v>-0.5054999999999999</v>
       </c>
       <c r="I5" t="n">
-        <v>0.9223</v>
+        <v>0.9283</v>
       </c>
       <c r="J5" t="n">
-        <v>0.09950000000000001</v>
+        <v>0.0922</v>
       </c>
       <c r="K5" t="n">
-        <v>0.0622</v>
+        <v>0.055</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0373</v>
+        <v>0.0372</v>
       </c>
       <c r="M5" t="n">
-        <v>0.3178</v>
+        <v>0.3306</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.5672</v>
+        <v>-0.5604</v>
       </c>
       <c r="O5" t="n">
-        <v>0.885</v>
+        <v>0.8911</v>
       </c>
       <c r="P5" t="n">
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R5" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="S5" t="n">
-        <v>0.1476</v>
+        <v>-0.0256</v>
       </c>
       <c r="T5" t="n">
-        <v>0.3871</v>
+        <v>0.1531</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.2395</v>
+        <v>-0.1786</v>
       </c>
       <c r="V5" t="n">
-        <v>0.1607</v>
+        <v>0.1578</v>
       </c>
       <c r="W5" t="n">
-        <v>0.1607</v>
+        <v>0.1578</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.2289</v>
+        <v>0.4597</v>
       </c>
       <c r="E6" t="n">
-        <v>0.7225</v>
+        <v>0.5477</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.4936</v>
+        <v>-0.08799999999999999</v>
       </c>
       <c r="G6" t="n">
-        <v>0.7884</v>
+        <v>0.8045</v>
       </c>
       <c r="H6" t="n">
-        <v>0.5698</v>
+        <v>0.5823</v>
       </c>
       <c r="I6" t="n">
-        <v>0.2186</v>
+        <v>0.2221</v>
       </c>
       <c r="J6" t="n">
-        <v>0.8404</v>
+        <v>0.8314</v>
       </c>
       <c r="K6" t="n">
-        <v>0.9177999999999999</v>
+        <v>0.9136</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.07729999999999999</v>
+        <v>-0.08210000000000001</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.0521</v>
+        <v>-0.027</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.348</v>
+        <v>-0.3312</v>
       </c>
       <c r="O6" t="n">
-        <v>0.2959</v>
+        <v>0.3043</v>
       </c>
       <c r="P6" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.9866</v>
+        <v>-0.7804</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.1179</v>
+        <v>-0.2837</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.8686</v>
+        <v>-0.4967</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.7071</v>
+        <v>-0.7025</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.7071</v>
+        <v>-0.7025</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>H. DRELL</t>
+          <t>R. RUBIO</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.0713</v>
+        <v>-1.4773</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.1552</v>
+        <v>-2.8152</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.916</v>
+        <v>1.3379</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.1478</v>
+        <v>-1.424</v>
       </c>
       <c r="H7" t="n">
-        <v>0.08939999999999999</v>
+        <v>-2.5115</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.2372</v>
+        <v>1.0875</v>
       </c>
       <c r="J7" t="n">
-        <v>0.3317</v>
+        <v>-3.0064</v>
       </c>
       <c r="K7" t="n">
-        <v>0.2944</v>
+        <v>-3.2145</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0373</v>
+        <v>0.2081</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.4795</v>
+        <v>1.5825</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.205</v>
+        <v>0.703</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.2745</v>
+        <v>0.8794999999999999</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.6805</v>
+        <v>-0.9105</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.1342</v>
+        <v>-3.6421</v>
       </c>
       <c r="R7" t="n">
-        <v>0.4537</v>
+        <v>2.7316</v>
       </c>
       <c r="S7" t="n">
-        <v>0.3033</v>
+        <v>-0.9348</v>
       </c>
       <c r="T7" t="n">
-        <v>0.6472</v>
+        <v>-0.2954</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.3439</v>
+        <v>-0.6394</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.5463</v>
+        <v>1.792</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>4.1287</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.5463</v>
+        <v>-2.3367</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>R. RUBIO</t>
+          <t>H. DRELL</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.807</v>
+        <v>-1.6331</v>
       </c>
       <c r="E8" t="n">
-        <v>-3.325</v>
+        <v>-0.6314</v>
       </c>
       <c r="F8" t="n">
-        <v>1.518</v>
+        <v>-1.0017</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.398</v>
+        <v>-0.1419</v>
       </c>
       <c r="H8" t="n">
-        <v>-2.4829</v>
+        <v>0.09180000000000001</v>
       </c>
       <c r="I8" t="n">
-        <v>1.0849</v>
+        <v>-0.2337</v>
       </c>
       <c r="J8" t="n">
-        <v>-2.9554</v>
+        <v>0.3303</v>
       </c>
       <c r="K8" t="n">
-        <v>-3.1738</v>
+        <v>0.293</v>
       </c>
       <c r="L8" t="n">
-        <v>0.2185</v>
+        <v>0.0372</v>
       </c>
       <c r="M8" t="n">
-        <v>1.5574</v>
+        <v>-0.4722</v>
       </c>
       <c r="N8" t="n">
-        <v>0.6909999999999999</v>
+        <v>-0.2012</v>
       </c>
       <c r="O8" t="n">
-        <v>0.8663999999999999</v>
+        <v>-0.271</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.9073</v>
+        <v>-0.6829</v>
       </c>
       <c r="Q8" t="n">
-        <v>-3.6293</v>
+        <v>-1.1382</v>
       </c>
       <c r="R8" t="n">
-        <v>2.722</v>
+        <v>0.4553</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.3014</v>
+        <v>-0.2636</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.8861</v>
+        <v>0.1765</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.4153</v>
+        <v>-0.44</v>
       </c>
       <c r="V8" t="n">
-        <v>1.7997</v>
+        <v>-0.5447</v>
       </c>
       <c r="W8" t="n">
-        <v>4.1458</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-2.3461</v>
+        <v>-0.5447</v>
       </c>
     </row>
     <row r="9">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.8929</v>
+        <v>-1.8261</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.5481</v>
+        <v>-1.5494</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.3448</v>
+        <v>-0.2767</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.2649</v>
+        <v>-1.2626</v>
       </c>
       <c r="H9" t="n">
-        <v>1.7632</v>
+        <v>1.7689</v>
       </c>
       <c r="I9" t="n">
-        <v>-3.0281</v>
+        <v>-3.0315</v>
       </c>
       <c r="J9" t="n">
-        <v>-1.0128</v>
+        <v>-1.0357</v>
       </c>
       <c r="K9" t="n">
-        <v>2.0953</v>
+        <v>2.0857</v>
       </c>
       <c r="L9" t="n">
-        <v>-3.1081</v>
+        <v>-3.1213</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.2521</v>
+        <v>-0.227</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.3321</v>
+        <v>-0.3168</v>
       </c>
       <c r="O9" t="n">
-        <v>0.08</v>
+        <v>0.0898</v>
       </c>
       <c r="P9" t="n">
-        <v>2.2683</v>
+        <v>2.2763</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="R9" t="n">
-        <v>2.4952</v>
+        <v>2.5039</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.711</v>
+        <v>-0.6608000000000001</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.3085</v>
+        <v>-0.2861</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.4026</v>
+        <v>-0.3747</v>
       </c>
       <c r="V9" t="n">
-        <v>-2.1853</v>
+        <v>-2.1789</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-2.1853</v>
+        <v>-2.1789</v>
       </c>
     </row>
     <row r="10">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.2112</v>
+        <v>-2.9381</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.3416</v>
+        <v>-3.0595</v>
       </c>
       <c r="F10" t="n">
-        <v>0.1304</v>
+        <v>0.1214</v>
       </c>
       <c r="G10" t="n">
-        <v>-1.1011</v>
+        <v>-1.1027</v>
       </c>
       <c r="H10" t="n">
-        <v>1.3592</v>
+        <v>1.3613</v>
       </c>
       <c r="I10" t="n">
-        <v>-2.4603</v>
+        <v>-2.464</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.8298</v>
+        <v>-0.8466</v>
       </c>
       <c r="K10" t="n">
-        <v>1.4546</v>
+        <v>1.4479</v>
       </c>
       <c r="L10" t="n">
-        <v>-2.2844</v>
+        <v>-2.2945</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.2712</v>
+        <v>-0.2562</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.0954</v>
+        <v>-0.0866</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.1759</v>
+        <v>-0.1695</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.361</v>
+        <v>-1.3658</v>
       </c>
       <c r="R10" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.405</v>
+        <v>-0.1312</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.7652</v>
+        <v>-0.4601</v>
       </c>
       <c r="U10" t="n">
-        <v>0.3602</v>
+        <v>0.3289</v>
       </c>
       <c r="V10" t="n">
-        <v>-1.4783</v>
+        <v>-1.4764</v>
       </c>
       <c r="W10" t="n">
-        <v>-0.3856</v>
+        <v>-0.387</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="11">
@@ -1267,64 +1267,64 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.8736</v>
+        <v>-3.0432</v>
       </c>
       <c r="E11" t="n">
-        <v>-5.1707</v>
+        <v>-4.5635</v>
       </c>
       <c r="F11" t="n">
-        <v>1.2972</v>
+        <v>1.5203</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.9953</v>
+        <v>-0.9936</v>
       </c>
       <c r="H11" t="n">
-        <v>0.4948</v>
+        <v>0.5022</v>
       </c>
       <c r="I11" t="n">
-        <v>-1.4901</v>
+        <v>-1.4958</v>
       </c>
       <c r="J11" t="n">
-        <v>-1.1087</v>
+        <v>-1.1406</v>
       </c>
       <c r="K11" t="n">
-        <v>1.0319</v>
+        <v>1.0202</v>
       </c>
       <c r="L11" t="n">
-        <v>-2.1406</v>
+        <v>-2.1608</v>
       </c>
       <c r="M11" t="n">
-        <v>0.1134</v>
+        <v>0.147</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.5371</v>
+        <v>-0.518</v>
       </c>
       <c r="O11" t="n">
-        <v>0.6505</v>
+        <v>0.665</v>
       </c>
       <c r="P11" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="Q11" t="n">
-        <v>-4.5367</v>
+        <v>-4.5526</v>
       </c>
       <c r="R11" t="n">
-        <v>2.2683</v>
+        <v>2.2763</v>
       </c>
       <c r="S11" t="n">
-        <v>-2.249</v>
+        <v>-1.4075</v>
       </c>
       <c r="T11" t="n">
-        <v>-1.1644</v>
+        <v>-0.5044999999999999</v>
       </c>
       <c r="U11" t="n">
-        <v>-1.0846</v>
+        <v>-0.903</v>
       </c>
       <c r="V11" t="n">
-        <v>1.639</v>
+        <v>1.6342</v>
       </c>
       <c r="W11" t="n">
-        <v>1.639</v>
+        <v>1.6342</v>
       </c>
       <c r="X11" t="n">
         <v>0</v>
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-5.7294</v>
+        <v>-5.468</v>
       </c>
       <c r="E12" t="n">
-        <v>-5.3505</v>
+        <v>-5.1194</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.3788</v>
+        <v>-0.3486</v>
       </c>
       <c r="G12" t="n">
-        <v>-2.2953</v>
+        <v>-2.2906</v>
       </c>
       <c r="H12" t="n">
-        <v>-2.4286</v>
+        <v>-2.4215</v>
       </c>
       <c r="I12" t="n">
-        <v>0.1333</v>
+        <v>0.131</v>
       </c>
       <c r="J12" t="n">
-        <v>-1.8301</v>
+        <v>-1.8463</v>
       </c>
       <c r="K12" t="n">
-        <v>-1.4515</v>
+        <v>-1.4586</v>
       </c>
       <c r="L12" t="n">
-        <v>-0.3786</v>
+        <v>-0.3877</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.4653</v>
+        <v>-0.4442</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.9771</v>
+        <v>-0.9629</v>
       </c>
       <c r="O12" t="n">
-        <v>0.5118</v>
+        <v>0.5187</v>
       </c>
       <c r="P12" t="n">
-        <v>-0.9073</v>
+        <v>-0.9105</v>
       </c>
       <c r="Q12" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R12" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.2733</v>
+        <v>-1.0197</v>
       </c>
       <c r="T12" t="n">
-        <v>-1.2521</v>
+        <v>-0.9968</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.0212</v>
+        <v>-0.0229</v>
       </c>
       <c r="V12" t="n">
-        <v>-1.2534</v>
+        <v>-1.2472</v>
       </c>
       <c r="W12" t="n">
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>-1.2534</v>
+        <v>-1.2472</v>
       </c>
     </row>
     <row r="13">
@@ -1423,67 +1423,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-5.9887</v>
+        <v>-5.299100000000001</v>
       </c>
       <c r="E13" t="n">
-        <v>-13.578</v>
+        <v>-13.1929</v>
       </c>
       <c r="F13" t="n">
-        <v>7.5896</v>
+        <v>7.8938</v>
       </c>
       <c r="G13" t="n">
-        <v>0.4384000000000001</v>
+        <v>0.4411999999999998</v>
       </c>
       <c r="H13" t="n">
-        <v>1.024800000000001</v>
+        <v>1.0063</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.5862000000000005</v>
+        <v>-0.565099999999999</v>
       </c>
       <c r="J13" t="n">
-        <v>-0.7176999999999998</v>
+        <v>-0.9470000000000007</v>
       </c>
       <c r="K13" t="n">
-        <v>4.107699999999999</v>
+        <v>3.9574</v>
       </c>
       <c r="L13" t="n">
-        <v>-4.8252</v>
+        <v>-4.9044</v>
       </c>
       <c r="M13" t="n">
-        <v>1.1562</v>
+        <v>1.3881</v>
       </c>
       <c r="N13" t="n">
-        <v>-3.0828</v>
+        <v>-2.951000000000001</v>
       </c>
       <c r="O13" t="n">
-        <v>4.2389</v>
+        <v>4.339399999999999</v>
       </c>
       <c r="P13" t="n">
-        <v>2.268400000000001</v>
+        <v>2.2764</v>
       </c>
       <c r="Q13" t="n">
-        <v>-15.8783</v>
+        <v>-15.9342</v>
       </c>
       <c r="R13" t="n">
-        <v>18.1469</v>
+        <v>18.2107</v>
       </c>
       <c r="S13" t="n">
-        <v>-6.8958</v>
+        <v>-6.2245</v>
       </c>
       <c r="T13" t="n">
-        <v>-3.7956</v>
+        <v>-3.0927</v>
       </c>
       <c r="U13" t="n">
-        <v>-3.1003</v>
+        <v>-3.1317</v>
       </c>
       <c r="V13" t="n">
-        <v>-1.7997</v>
+        <v>-1.7917</v>
       </c>
       <c r="W13" t="n">
-        <v>6.813300000000001</v>
+        <v>6.781000000000001</v>
       </c>
       <c r="X13" t="n">
-        <v>-8.613099999999999</v>
+        <v>-8.572800000000001</v>
       </c>
     </row>
     <row r="14">
@@ -1501,67 +1501,67 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>3.9005</v>
+        <v>3.1415</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.7154</v>
+        <v>-1.1052</v>
       </c>
       <c r="F14" t="n">
-        <v>4.6159</v>
+        <v>4.2467</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.8816000000000001</v>
+        <v>-0.8735000000000001</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.2152</v>
+        <v>-0.2045</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.6664</v>
+        <v>-0.669</v>
       </c>
       <c r="J14" t="n">
-        <v>-1.5013</v>
+        <v>-1.5203</v>
       </c>
       <c r="K14" t="n">
-        <v>0.1487</v>
+        <v>0.1411</v>
       </c>
       <c r="L14" t="n">
-        <v>-1.6501</v>
+        <v>-1.6614</v>
       </c>
       <c r="M14" t="n">
-        <v>0.6197</v>
+        <v>0.6468</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.3639</v>
+        <v>-0.3457</v>
       </c>
       <c r="O14" t="n">
-        <v>0.9837</v>
+        <v>0.9925</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Q14" t="n">
-        <v>-2.4952</v>
+        <v>-2.5039</v>
       </c>
       <c r="R14" t="n">
-        <v>2.4952</v>
+        <v>2.5039</v>
       </c>
       <c r="S14" t="n">
-        <v>1.8897</v>
+        <v>1.1335</v>
       </c>
       <c r="T14" t="n">
-        <v>0.7743</v>
+        <v>0.4246</v>
       </c>
       <c r="U14" t="n">
-        <v>1.1154</v>
+        <v>0.709</v>
       </c>
       <c r="V14" t="n">
-        <v>2.8924</v>
+        <v>2.8814</v>
       </c>
       <c r="W14" t="n">
-        <v>2.5068</v>
+        <v>2.4945</v>
       </c>
       <c r="X14" t="n">
-        <v>0.3856</v>
+        <v>0.387</v>
       </c>
     </row>
     <row r="15">
@@ -1579,67 +1579,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3.1389</v>
+        <v>3.0956</v>
       </c>
       <c r="E15" t="n">
-        <v>0.9955000000000001</v>
+        <v>0.7377</v>
       </c>
       <c r="F15" t="n">
-        <v>2.1434</v>
+        <v>2.3578</v>
       </c>
       <c r="G15" t="n">
-        <v>1.5336</v>
+        <v>1.5287</v>
       </c>
       <c r="H15" t="n">
-        <v>2.0908</v>
+        <v>2.0936</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.5572</v>
+        <v>-0.5649</v>
       </c>
       <c r="J15" t="n">
-        <v>0.5867</v>
+        <v>0.5663</v>
       </c>
       <c r="K15" t="n">
-        <v>1.7144</v>
+        <v>1.7064</v>
       </c>
       <c r="L15" t="n">
-        <v>-1.1276</v>
+        <v>-1.1401</v>
       </c>
       <c r="M15" t="n">
-        <v>0.9469</v>
+        <v>0.9623</v>
       </c>
       <c r="N15" t="n">
-        <v>0.3764</v>
+        <v>0.3871</v>
       </c>
       <c r="O15" t="n">
-        <v>0.5705</v>
+        <v>0.5752</v>
       </c>
       <c r="P15" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="Q15" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="R15" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="S15" t="n">
-        <v>0.405</v>
+        <v>0.3589</v>
       </c>
       <c r="T15" t="n">
-        <v>0.4748</v>
+        <v>0.2413</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.0699</v>
+        <v>0.1176</v>
       </c>
       <c r="V15" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
       <c r="W15" t="n">
-        <v>0.1607</v>
+        <v>0.1578</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.3214</v>
+        <v>-0.3155</v>
       </c>
     </row>
     <row r="16">
@@ -1657,67 +1657,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.8332</v>
+        <v>1.9609</v>
       </c>
       <c r="E16" t="n">
-        <v>1.941</v>
+        <v>1.7963</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.1078</v>
+        <v>0.1646</v>
       </c>
       <c r="G16" t="n">
-        <v>2.9989</v>
+        <v>2.9939</v>
       </c>
       <c r="H16" t="n">
-        <v>2.3911</v>
+        <v>2.3815</v>
       </c>
       <c r="I16" t="n">
-        <v>0.6078</v>
+        <v>0.6124000000000001</v>
       </c>
       <c r="J16" t="n">
-        <v>2.5238</v>
+        <v>2.5054</v>
       </c>
       <c r="K16" t="n">
-        <v>2.4865</v>
+        <v>2.4681</v>
       </c>
       <c r="L16" t="n">
-        <v>0.0373</v>
+        <v>0.0372</v>
       </c>
       <c r="M16" t="n">
-        <v>0.4751</v>
+        <v>0.4886</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.0954</v>
+        <v>-0.0866</v>
       </c>
       <c r="O16" t="n">
-        <v>0.5705</v>
+        <v>0.5752</v>
       </c>
       <c r="P16" t="n">
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R16" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="S16" t="n">
-        <v>0.1518</v>
+        <v>0.2856</v>
       </c>
       <c r="T16" t="n">
-        <v>0.2299</v>
+        <v>0.1136</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.078</v>
+        <v>0.1721</v>
       </c>
       <c r="V16" t="n">
-        <v>-1.3176</v>
+        <v>-1.3187</v>
       </c>
       <c r="W16" t="n">
-        <v>0.3214</v>
+        <v>0.3155</v>
       </c>
       <c r="X16" t="n">
-        <v>-1.639</v>
+        <v>-1.6342</v>
       </c>
     </row>
     <row r="17">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.1693</v>
+        <v>1.1613</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.5334</v>
+        <v>-0.6685</v>
       </c>
       <c r="F17" t="n">
-        <v>1.7026</v>
+        <v>1.8297</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.6501</v>
+        <v>-0.6446</v>
       </c>
       <c r="H17" t="n">
-        <v>-1.5511</v>
+        <v>-1.5537</v>
       </c>
       <c r="I17" t="n">
-        <v>0.901</v>
+        <v>0.909</v>
       </c>
       <c r="J17" t="n">
-        <v>-1.3493</v>
+        <v>-1.3637</v>
       </c>
       <c r="K17" t="n">
-        <v>-1.424</v>
+        <v>-1.4381</v>
       </c>
       <c r="L17" t="n">
-        <v>0.0746</v>
+        <v>0.0745</v>
       </c>
       <c r="M17" t="n">
-        <v>0.6992</v>
+        <v>0.719</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.1272</v>
+        <v>-0.1155</v>
       </c>
       <c r="O17" t="n">
-        <v>0.8264</v>
+        <v>0.8345</v>
       </c>
       <c r="P17" t="n">
-        <v>1.8147</v>
+        <v>1.8211</v>
       </c>
       <c r="Q17" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="R17" t="n">
-        <v>2.0415</v>
+        <v>2.0487</v>
       </c>
       <c r="S17" t="n">
-        <v>0.5511</v>
+        <v>0.5296</v>
       </c>
       <c r="T17" t="n">
-        <v>0.3357</v>
+        <v>0.2203</v>
       </c>
       <c r="U17" t="n">
-        <v>0.2153</v>
+        <v>0.3093</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.5463</v>
+        <v>-0.5447</v>
       </c>
       <c r="W17" t="n">
-        <v>0.7071</v>
+        <v>0.7025</v>
       </c>
       <c r="X17" t="n">
-        <v>-1.2534</v>
+        <v>-1.2472</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>U. GARUBA</t>
+          <t>T. MALEDON</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>1.1236</v>
+        <v>0.8372000000000001</v>
       </c>
       <c r="E18" t="n">
-        <v>1.143</v>
+        <v>0.1558</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.0194</v>
+        <v>0.6814</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.5713</v>
+        <v>2.9728</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.8485</v>
+        <v>0.6462</v>
       </c>
       <c r="I18" t="n">
-        <v>0.2772</v>
+        <v>2.3266</v>
       </c>
       <c r="J18" t="n">
-        <v>0.4595</v>
+        <v>4.1618</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.2495</v>
+        <v>1.4511</v>
       </c>
       <c r="L18" t="n">
-        <v>0.709</v>
+        <v>2.7106</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.0308</v>
+        <v>-1.189</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.599</v>
+        <v>-0.805</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.4318</v>
+        <v>-0.384</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>-3.6421</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>-4.5526</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>0.9105</v>
       </c>
       <c r="S18" t="n">
-        <v>1.6949</v>
+        <v>0.5748</v>
       </c>
       <c r="T18" t="n">
-        <v>0.6835</v>
+        <v>0.0019</v>
       </c>
       <c r="U18" t="n">
-        <v>1.0114</v>
+        <v>0.5729</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>0.9317</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>0.5447</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>0.387</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A. ABALDE</t>
+          <t>F. CAMPAZZO</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,64 +1891,64 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.2764</v>
+        <v>0.4597</v>
       </c>
       <c r="E19" t="n">
-        <v>-2.6203</v>
+        <v>-4.0815</v>
       </c>
       <c r="F19" t="n">
-        <v>2.8967</v>
+        <v>4.5412</v>
       </c>
       <c r="G19" t="n">
-        <v>-1.619</v>
+        <v>0.0752</v>
       </c>
       <c r="H19" t="n">
-        <v>0.09229999999999999</v>
+        <v>0.3126</v>
       </c>
       <c r="I19" t="n">
-        <v>-1.7113</v>
+        <v>-0.2374</v>
       </c>
       <c r="J19" t="n">
-        <v>-2.4328</v>
+        <v>-1.4611</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.111</v>
+        <v>0.1411</v>
       </c>
       <c r="L19" t="n">
-        <v>-2.3218</v>
+        <v>-1.6023</v>
       </c>
       <c r="M19" t="n">
-        <v>0.8138</v>
+        <v>1.5363</v>
       </c>
       <c r="N19" t="n">
-        <v>0.2033</v>
+        <v>0.1715</v>
       </c>
       <c r="O19" t="n">
-        <v>0.6105</v>
+        <v>1.3648</v>
       </c>
       <c r="P19" t="n">
-        <v>1.8147</v>
+        <v>-2.0487</v>
       </c>
       <c r="Q19" t="n">
-        <v>-0.2268</v>
+        <v>-4.7803</v>
       </c>
       <c r="R19" t="n">
-        <v>2.0415</v>
+        <v>2.7316</v>
       </c>
       <c r="S19" t="n">
-        <v>0.0808</v>
+        <v>0.2543</v>
       </c>
       <c r="T19" t="n">
-        <v>0.0393</v>
+        <v>-0.019</v>
       </c>
       <c r="U19" t="n">
-        <v>0.0414</v>
+        <v>0.2733</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>2.1789</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>2.1789</v>
       </c>
       <c r="X19" t="n">
         <v>0</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>T. MALEDON</t>
+          <t>U. GARUBA</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>0.2286</v>
+        <v>0.4584</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.3938</v>
+        <v>0.9026</v>
       </c>
       <c r="F20" t="n">
-        <v>0.6224</v>
+        <v>-0.4442</v>
       </c>
       <c r="G20" t="n">
-        <v>2.9746</v>
+        <v>-0.5659999999999999</v>
       </c>
       <c r="H20" t="n">
-        <v>0.645</v>
+        <v>-0.8446</v>
       </c>
       <c r="I20" t="n">
-        <v>2.3296</v>
+        <v>0.2786</v>
       </c>
       <c r="J20" t="n">
-        <v>4.1862</v>
+        <v>0.4522</v>
       </c>
       <c r="K20" t="n">
-        <v>1.4648</v>
+        <v>-0.2553</v>
       </c>
       <c r="L20" t="n">
-        <v>2.7214</v>
+        <v>0.7075</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.2116</v>
+        <v>-1.0182</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.8198</v>
+        <v>-0.5893</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.3918</v>
+        <v>-0.4289</v>
       </c>
       <c r="P20" t="n">
-        <v>-3.6293</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>-4.5367</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>0.9073</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.0487</v>
+        <v>1.0243</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.5898</v>
+        <v>0.4504</v>
       </c>
       <c r="U20" t="n">
-        <v>0.5411</v>
+        <v>0.574</v>
       </c>
       <c r="V20" t="n">
-        <v>0.9320000000000001</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>0.5463</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>0.3856</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>S. LLULL</t>
+          <t>A. ABALDE</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>0.075</v>
+        <v>0.3822</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.2472</v>
+        <v>-2.6353</v>
       </c>
       <c r="F21" t="n">
-        <v>0.3223</v>
+        <v>3.0175</v>
       </c>
       <c r="G21" t="n">
-        <v>0.6077</v>
+        <v>-1.6142</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.4372</v>
+        <v>0.0974</v>
       </c>
       <c r="I21" t="n">
-        <v>1.0449</v>
+        <v>-1.7116</v>
       </c>
       <c r="J21" t="n">
-        <v>0.4121</v>
+        <v>-2.4491</v>
       </c>
       <c r="K21" t="n">
-        <v>0.1936</v>
+        <v>-0.1174</v>
       </c>
       <c r="L21" t="n">
-        <v>0.2185</v>
+        <v>-2.3317</v>
       </c>
       <c r="M21" t="n">
-        <v>0.1956</v>
+        <v>0.8349</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.6308</v>
+        <v>0.2148</v>
       </c>
       <c r="O21" t="n">
-        <v>0.8264</v>
+        <v>0.6201</v>
       </c>
       <c r="P21" t="n">
-        <v>0.2268</v>
+        <v>1.8211</v>
       </c>
       <c r="Q21" t="n">
-        <v>-1.1342</v>
+        <v>-0.2276</v>
       </c>
       <c r="R21" t="n">
-        <v>1.361</v>
+        <v>2.0487</v>
       </c>
       <c r="S21" t="n">
-        <v>0.8794999999999999</v>
+        <v>0.1754</v>
       </c>
       <c r="T21" t="n">
-        <v>0.4748</v>
+        <v>0.0414</v>
       </c>
       <c r="U21" t="n">
-        <v>0.4047</v>
+        <v>0.1339</v>
       </c>
       <c r="V21" t="n">
-        <v>-1.639</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.639</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>G. DECK</t>
+          <t>S. LLULL</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.2722</v>
+        <v>0.2606</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.384</v>
+        <v>-0.1546</v>
       </c>
       <c r="F22" t="n">
-        <v>0.1118</v>
+        <v>0.4151</v>
       </c>
       <c r="G22" t="n">
-        <v>-3.3885</v>
+        <v>0.6032999999999999</v>
       </c>
       <c r="H22" t="n">
-        <v>-3.0446</v>
+        <v>-0.4393</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.3439</v>
+        <v>1.0426</v>
       </c>
       <c r="J22" t="n">
-        <v>-2.4596</v>
+        <v>0.387</v>
       </c>
       <c r="K22" t="n">
-        <v>-2.193</v>
+        <v>0.1789</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.2666</v>
+        <v>0.2081</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.9288999999999999</v>
+        <v>0.2164</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.8516</v>
+        <v>-0.6182</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.0772</v>
+        <v>0.8345</v>
       </c>
       <c r="P22" t="n">
-        <v>0.6805</v>
+        <v>0.2276</v>
       </c>
       <c r="Q22" t="n">
+        <v>-1.1382</v>
+      </c>
+      <c r="R22" t="n">
+        <v>1.3658</v>
+      </c>
+      <c r="S22" t="n">
+        <v>1.0638</v>
+      </c>
+      <c r="T22" t="n">
+        <v>0.5966</v>
+      </c>
+      <c r="U22" t="n">
+        <v>0.4672</v>
+      </c>
+      <c r="V22" t="n">
+        <v>-1.6342</v>
+      </c>
+      <c r="W22" t="n">
         <v>0</v>
       </c>
-      <c r="R22" t="n">
-        <v>0.6805</v>
-      </c>
-      <c r="S22" t="n">
-        <v>1.3432</v>
-      </c>
-      <c r="T22" t="n">
-        <v>0.983</v>
-      </c>
-      <c r="U22" t="n">
-        <v>0.3602</v>
-      </c>
-      <c r="V22" t="n">
-        <v>1.0927</v>
-      </c>
-      <c r="W22" t="n">
-        <v>1.0927</v>
-      </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>-1.6342</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>F. CAMPAZZO</t>
+          <t>G. DECK</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,64 +2203,64 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.6067</v>
+        <v>-0.3399</v>
       </c>
       <c r="E23" t="n">
-        <v>-4.7391</v>
+        <v>-0.7634</v>
       </c>
       <c r="F23" t="n">
-        <v>4.1325</v>
+        <v>0.4235</v>
       </c>
       <c r="G23" t="n">
-        <v>0.0803</v>
+        <v>-3.3885</v>
       </c>
       <c r="H23" t="n">
-        <v>0.3043</v>
+        <v>-3.0444</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.224</v>
+        <v>-0.3441</v>
       </c>
       <c r="J23" t="n">
-        <v>-1.4321</v>
+        <v>-2.4865</v>
       </c>
       <c r="K23" t="n">
-        <v>0.1487</v>
+        <v>-2.2105</v>
       </c>
       <c r="L23" t="n">
-        <v>-1.5808</v>
+        <v>-0.276</v>
       </c>
       <c r="M23" t="n">
-        <v>1.5124</v>
+        <v>-0.902</v>
       </c>
       <c r="N23" t="n">
-        <v>0.1556</v>
+        <v>-0.8339</v>
       </c>
       <c r="O23" t="n">
-        <v>1.3568</v>
+        <v>-0.06809999999999999</v>
       </c>
       <c r="P23" t="n">
-        <v>-2.0415</v>
+        <v>0.6829</v>
       </c>
       <c r="Q23" t="n">
-        <v>-4.7635</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>2.722</v>
+        <v>0.6829</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.8308</v>
+        <v>1.2762</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.7289</v>
+        <v>0.6337</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.1019</v>
+        <v>0.6425999999999999</v>
       </c>
       <c r="V23" t="n">
-        <v>2.1853</v>
+        <v>1.0895</v>
       </c>
       <c r="W23" t="n">
-        <v>2.1853</v>
+        <v>1.0895</v>
       </c>
       <c r="X23" t="n">
         <v>0</v>
@@ -2281,64 +2281,64 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-1.7501</v>
+        <v>-1.3923</v>
       </c>
       <c r="E24" t="n">
-        <v>-1.6773</v>
+        <v>-1.4542</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.0728</v>
+        <v>0.0619</v>
       </c>
       <c r="G24" t="n">
-        <v>-1.1297</v>
+        <v>-1.1253</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.3594</v>
+        <v>-0.3536</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.7703</v>
+        <v>-0.7717000000000001</v>
       </c>
       <c r="J24" t="n">
-        <v>-0.6771</v>
+        <v>-0.6807</v>
       </c>
       <c r="K24" t="n">
-        <v>0.0346</v>
+        <v>0.0345</v>
       </c>
       <c r="L24" t="n">
-        <v>-0.7117</v>
+        <v>-0.7151999999999999</v>
       </c>
       <c r="M24" t="n">
-        <v>-0.4526</v>
+        <v>-0.4446</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.394</v>
+        <v>-0.3881</v>
       </c>
       <c r="O24" t="n">
-        <v>-0.0586</v>
+        <v>-0.0565</v>
       </c>
       <c r="P24" t="n">
-        <v>-2.0415</v>
+        <v>-2.0487</v>
       </c>
       <c r="Q24" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R24" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="S24" t="n">
-        <v>0.3285</v>
+        <v>0.6922</v>
       </c>
       <c r="T24" t="n">
-        <v>0.1754</v>
+        <v>0.4133</v>
       </c>
       <c r="U24" t="n">
-        <v>0.153</v>
+        <v>0.2788</v>
       </c>
       <c r="V24" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="W24" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X24" t="n">
         <v>0</v>
@@ -2359,67 +2359,67 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-3.1279</v>
+        <v>-3.2393</v>
       </c>
       <c r="E25" t="n">
-        <v>-0.1977</v>
+        <v>-0.4661</v>
       </c>
       <c r="F25" t="n">
-        <v>-2.9302</v>
+        <v>-2.7732</v>
       </c>
       <c r="G25" t="n">
-        <v>-0.3935</v>
+        <v>-0.4029</v>
       </c>
       <c r="H25" t="n">
-        <v>-0.09229999999999999</v>
+        <v>-0.0974</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.3012</v>
+        <v>-0.3056</v>
       </c>
       <c r="J25" t="n">
-        <v>0.5276999999999999</v>
+        <v>0.5006</v>
       </c>
       <c r="K25" t="n">
-        <v>0.8689</v>
+        <v>0.8511</v>
       </c>
       <c r="L25" t="n">
-        <v>-0.3413</v>
+        <v>-0.3505</v>
       </c>
       <c r="M25" t="n">
-        <v>-0.9212</v>
+        <v>-0.9036</v>
       </c>
       <c r="N25" t="n">
-        <v>-0.9612000000000001</v>
+        <v>-0.9485</v>
       </c>
       <c r="O25" t="n">
-        <v>0.04</v>
+        <v>0.0449</v>
       </c>
       <c r="P25" t="n">
-        <v>-0.4537</v>
+        <v>-0.4553</v>
       </c>
       <c r="Q25" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R25" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="S25" t="n">
-        <v>0.4509</v>
+        <v>0.3425</v>
       </c>
       <c r="T25" t="n">
-        <v>0.248</v>
+        <v>0.0136</v>
       </c>
       <c r="U25" t="n">
-        <v>0.2029</v>
+        <v>0.3289</v>
       </c>
       <c r="V25" t="n">
-        <v>-2.7317</v>
+        <v>-2.7237</v>
       </c>
       <c r="W25" t="n">
-        <v>0.1607</v>
+        <v>0.1578</v>
       </c>
       <c r="X25" t="n">
-        <v>-2.8924</v>
+        <v>-2.8814</v>
       </c>
     </row>
     <row r="26">
@@ -2437,67 +2437,67 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>5.9886</v>
+        <v>6.7859</v>
       </c>
       <c r="E26" t="n">
-        <v>-7.428699999999999</v>
+        <v>-7.736400000000001</v>
       </c>
       <c r="F26" t="n">
-        <v>13.4174</v>
+        <v>14.522</v>
       </c>
       <c r="G26" t="n">
-        <v>-0.4386000000000006</v>
+        <v>-0.4411</v>
       </c>
       <c r="H26" t="n">
-        <v>-1.0248</v>
+        <v>-1.006200000000001</v>
       </c>
       <c r="I26" t="n">
-        <v>0.5861999999999999</v>
+        <v>0.5648999999999998</v>
       </c>
       <c r="J26" t="n">
-        <v>-1.1562</v>
+        <v>-1.3881</v>
       </c>
       <c r="K26" t="n">
-        <v>3.0827</v>
+        <v>2.951</v>
       </c>
       <c r="L26" t="n">
-        <v>-4.2391</v>
+        <v>-4.3393</v>
       </c>
       <c r="M26" t="n">
-        <v>0.7175999999999998</v>
+        <v>0.9468999999999999</v>
       </c>
       <c r="N26" t="n">
-        <v>-4.1076</v>
+        <v>-3.9574</v>
       </c>
       <c r="O26" t="n">
-        <v>4.8254</v>
+        <v>4.9042</v>
       </c>
       <c r="P26" t="n">
-        <v>-2.2683</v>
+        <v>-2.276300000000001</v>
       </c>
       <c r="Q26" t="n">
-        <v>-18.1467</v>
+        <v>-18.2105</v>
       </c>
       <c r="R26" t="n">
-        <v>15.8783</v>
+        <v>15.9342</v>
       </c>
       <c r="S26" t="n">
-        <v>6.8959</v>
+        <v>7.7111</v>
       </c>
       <c r="T26" t="n">
-        <v>3.100000000000001</v>
+        <v>3.1317</v>
       </c>
       <c r="U26" t="n">
-        <v>3.7956</v>
+        <v>4.5796</v>
       </c>
       <c r="V26" t="n">
-        <v>1.799799999999999</v>
+        <v>1.7919</v>
       </c>
       <c r="W26" t="n">
-        <v>8.7737</v>
+        <v>8.730700000000001</v>
       </c>
       <c r="X26" t="n">
-        <v>-6.974</v>
+        <v>-6.9385</v>
       </c>
     </row>
   </sheetData>

--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104512_W6.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104512_W6.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X26"/>
+  <dimension ref="A1:Y26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,6 +632,11 @@
       <c r="X2" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_104512_W6.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -705,6 +715,11 @@
       <c r="X3" t="n">
         <v>1.1609</v>
       </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_104512_W6.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -783,6 +798,11 @@
       <c r="X4" t="n">
         <v>-0.5447</v>
       </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_104512_W6.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -861,6 +881,11 @@
       <c r="X5" t="n">
         <v>0</v>
       </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_104512_W6.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -939,6 +964,11 @@
       <c r="X6" t="n">
         <v>-0.7025</v>
       </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_104512_W6.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1017,6 +1047,11 @@
       <c r="X7" t="n">
         <v>-2.3367</v>
       </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_104512_W6.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1095,6 +1130,11 @@
       <c r="X8" t="n">
         <v>-0.5447</v>
       </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_104512_W6.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1173,6 +1213,11 @@
       <c r="X9" t="n">
         <v>-2.1789</v>
       </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_104512_W6.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1251,6 +1296,11 @@
       <c r="X10" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_104512_W6.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1329,6 +1379,11 @@
       <c r="X11" t="n">
         <v>0</v>
       </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_104512_W6.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1407,6 +1462,11 @@
       <c r="X12" t="n">
         <v>-1.2472</v>
       </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>play_by_play_104512_W6.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1485,6 +1545,7 @@
       <c r="X13" t="n">
         <v>-8.572800000000001</v>
       </c>
+      <c r="Y13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1563,6 +1624,11 @@
       <c r="X14" t="n">
         <v>0.387</v>
       </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>play_by_play_104512_W6.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1641,6 +1707,11 @@
       <c r="X15" t="n">
         <v>-0.3155</v>
       </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_104512_W6.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1719,6 +1790,11 @@
       <c r="X16" t="n">
         <v>-1.6342</v>
       </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_104512_W6.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1797,6 +1873,11 @@
       <c r="X17" t="n">
         <v>-1.2472</v>
       </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_104512_W6.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1875,6 +1956,11 @@
       <c r="X18" t="n">
         <v>0.387</v>
       </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_104512_W6.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1953,6 +2039,11 @@
       <c r="X19" t="n">
         <v>0</v>
       </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_104512_W6.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2031,6 +2122,11 @@
       <c r="X20" t="n">
         <v>0</v>
       </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_104512_W6.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2109,6 +2205,11 @@
       <c r="X21" t="n">
         <v>0</v>
       </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_104512_W6.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2187,6 +2288,11 @@
       <c r="X22" t="n">
         <v>-1.6342</v>
       </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_104512_W6.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2265,6 +2371,11 @@
       <c r="X23" t="n">
         <v>0</v>
       </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_104512_W6.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2343,6 +2454,11 @@
       <c r="X24" t="n">
         <v>0</v>
       </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>play_by_play_104512_W6.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2421,6 +2537,11 @@
       <c r="X25" t="n">
         <v>-2.8814</v>
       </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>play_by_play_104512_W6.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2499,6 +2620,7 @@
       <c r="X26" t="n">
         <v>-6.9385</v>
       </c>
+      <c r="Y26" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
